--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N71_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.83182186100347</v>
+        <v>6.635171052413064</v>
       </c>
       <c r="D2" t="n">
-        <v>40.741954747742</v>
+        <v>6.620567646508075</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
